--- a/proposals/2026-11_nlrc-ai-labor-commission/제안요청_준수표.xlsx
+++ b/proposals/2026-11_nlrc-ai-labor-commission/제안요청_준수표.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="62" customHeight="1">
+    <row r="4" ht="104" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CSR-001</t>
@@ -552,13 +552,16 @@
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 1.1.1 사업 개요
 Ⅱ. 전략 및 방법론 &gt; 1.2.1 1차 사업의 한계와 2차 사업 개선 목표
+Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
 Ⅱ. 전략 및 방법론 &gt; 1.3.1 제안의 목적과 범위
-Ⅱ. 전략 및 방법론 &gt; 2.2.1 AI 노동위원회 · 노사마루 통합 추진 단계</t>
+Ⅱ. 전략 및 방법론 &gt; 2.2.1 AI 노동위원회 · 노사마루 통합 추진 단계
+Ⅱ. 전략 및 방법론 &gt; 2.2.2 1차 산출물 인수 및 1차 사업 연속성 확보
+Ⅷ. 기타 사항 &gt; 2.1.2 3차 사업계획 및 제안요청서 작성 (CSR-001)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>15~17, 20</t>
+          <t>15~18, 21~22, 85</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -568,7 +571,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ECR-001</t>
@@ -581,12 +584,14 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Ⅲ. 기술 및 기능 &gt; 1.1.1 별도 장비 확장 없는 자원 구성 및 최적화 방안</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
+Ⅲ. 기술 및 기능 &gt; 1.1.1 별도 장비 확장 없는 자원 구성 및 최적화 방안
+Ⅲ. 기술 및 기능 &gt; 1.1.2 GPU 자원 배치 및 신규 기능 수용 방안</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17, 29~30</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -616,7 +621,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>17~18, 39</t>
+          <t>18~19, 42</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -644,7 +649,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -672,7 +677,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -700,7 +705,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -728,7 +733,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -756,7 +761,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -786,7 +791,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>23, 41, 62</t>
+          <t>25, 44, 65</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -814,7 +819,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -843,7 +848,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>23, 43</t>
+          <t>25, 46</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>23, 44</t>
+          <t>25, 47</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -900,7 +905,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -928,7 +933,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -956,7 +961,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1012,7 +1017,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1040,7 +1045,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1069,7 +1074,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>22, 28</t>
+          <t>24, 31</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1097,7 +1102,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1125,7 +1130,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1135,7 +1140,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="34" customHeight="1">
+    <row r="25" ht="48" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
           <t>SFR-020</t>
@@ -1149,12 +1154,13 @@
       <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 3.1.1 문서 전처리 개선 · Graph DB · 문서초안 고도화 기술
+Ⅲ. 기술 및 기능 &gt; 1.1.2 GPU 자원 배치 및 신규 기능 수용 방안
 Ⅲ. 기술 및 기능 &gt; 2.2.1 비정형 문서 전처리 및 구조 분석</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>22, 32</t>
+          <t>24, 30, 35</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1164,7 +1170,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="34" customHeight="1">
+    <row r="26" ht="48" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>SFR-021</t>
@@ -1178,12 +1184,13 @@
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 3.1.1 문서 전처리 개선 · Graph DB · 문서초안 고도화 기술
+Ⅲ. 기술 및 기능 &gt; 1.1.2 GPU 자원 배치 및 신규 기능 수용 방안
 Ⅲ. 기술 및 기능 &gt; 2.2.2 언어모델 성능 고도화</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>22, 33</t>
+          <t>24, 30, 36</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1211,7 +1218,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1239,7 +1246,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1267,7 +1274,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1295,7 +1302,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1323,7 +1330,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1333,7 +1340,7 @@
       </c>
       <c r="F31" s="6" t="inlineStr"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="34" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>SFR-027</t>
@@ -1346,12 +1353,13 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Ⅲ. 기술 및 기능 &gt; 2.2.6 음성 자료 분석 고도화 · 참조문서 관리체계</t>
+          <t>Ⅲ. 기술 및 기능 &gt; 1.1.2 GPU 자원 배치 및 신규 기능 수용 방안
+Ⅲ. 기술 및 기능 &gt; 2.2.6 음성 자료 분석 고도화 · 참조문서 관리체계</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30, 40</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1379,7 +1387,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1407,7 +1415,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1435,7 +1443,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1445,7 +1453,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr"/>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="34" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>PER-002</t>
@@ -1458,12 +1466,13 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Ⅳ. 성능 및 품질 &gt; 1.1.1 1차 사업 대비 평균 처리시간 30% 이상 단축 방안</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
+Ⅳ. 성능 및 품질 &gt; 1.1.1 1차 사업 대비 평균 처리시간 30% 이상 단축 방안</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>17, 58</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1473,7 +1482,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr"/>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37" ht="34" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>PER-003</t>
@@ -1486,12 +1495,13 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Ⅳ. 성능 및 품질 &gt; 1.2.1 대용량 첨부파일 처리 · 토큰 한계로 인한 품질 저하 방지</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
+Ⅳ. 성능 및 품질 &gt; 1.2.1 대용량 첨부파일 처리 · 토큰 한계로 인한 품질 저하 방지</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>17, 59</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1519,7 +1529,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1547,7 +1557,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1575,7 +1585,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1603,7 +1613,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1634,7 +1644,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>18, 23, 61~62</t>
+          <t>19, 25, 64~65</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1663,7 +1673,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>49, 67</t>
+          <t>52, 70</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1692,7 +1702,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>47, 49</t>
+          <t>50, 52</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1720,7 +1730,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1748,7 +1758,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1776,7 +1786,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1804,7 +1814,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1832,7 +1842,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1860,7 +1870,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1888,7 +1898,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1916,7 +1926,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1945,7 +1955,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>59~60</t>
+          <t>62~63</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -1973,7 +1983,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2001,7 +2011,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2029,7 +2039,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2057,7 +2067,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2085,7 +2095,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2113,7 +2123,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2142,7 +2152,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>47, 76</t>
+          <t>50, 79</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2171,7 +2181,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>46~47</t>
+          <t>49~50</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2200,7 +2210,7 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>58, 72</t>
+          <t>61, 75</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2228,7 +2238,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2256,7 +2266,7 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2284,7 +2294,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2312,7 +2322,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2341,7 +2351,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>24, 52</t>
+          <t>26, 55</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2369,7 +2379,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2398,7 +2408,7 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>24, 53</t>
+          <t>26, 56</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2426,7 +2436,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2436,7 +2446,7 @@
       </c>
       <c r="F70" s="6" t="inlineStr"/>
     </row>
-    <row r="71" ht="34" customHeight="1">
+    <row r="71" ht="48" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>COR-007</t>
@@ -2449,13 +2459,14 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Ⅲ. 기술 및 기능 &gt; 5.1.2 표준 프레임워크 · 손해배상 · 지식재산권
+          <t>Ⅱ. 전략 및 방법론 &gt; 2.2.2 1차 산출물 인수 및 1차 사업 연속성 확보
+Ⅲ. 기술 및 기능 &gt; 5.1.2 표준 프레임워크 · 손해배상 · 지식재산권
 Ⅵ. 프로젝트 지원 &gt; 4.1.1 기밀보안 체계 · 저작권 · 개인정보보호 · 비상대책</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>53, 76</t>
+          <t>22, 56, 79</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2485,7 +2496,7 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>11, 13, 67</t>
+          <t>11, 13, 70</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2543,7 +2554,7 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>12, 78</t>
+          <t>12, 81</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2571,7 +2582,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2599,7 +2610,7 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2627,7 +2638,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2657,7 +2668,7 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>25, 65~66</t>
+          <t>27, 68~69</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2685,7 +2696,7 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2713,7 +2724,7 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2741,7 +2752,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2769,7 +2780,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2779,7 +2790,7 @@
       </c>
       <c r="F82" s="6" t="inlineStr"/>
     </row>
-    <row r="83" ht="20" customHeight="1">
+    <row r="83" ht="34" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
           <t>PSR-003</t>
@@ -2792,12 +2803,13 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Ⅵ. 프로젝트 지원 &gt; 3.1.1 대상자별 교육훈련 · 매뉴얼 · 기술이전</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 2.2.2 1차 산출물 인수 및 1차 사업 연속성 확보
+Ⅵ. 프로젝트 지원 &gt; 3.1.1 대상자별 교육훈련 · 매뉴얼 · 기술이전</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>22, 77</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2825,7 +2837,7 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2854,7 +2866,7 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>67, 80</t>
+          <t>70, 83</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2882,7 +2894,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2910,7 +2922,7 @@
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">

--- a/proposals/2026-11_nlrc-ai-labor-commission/제안요청_준수표.xlsx
+++ b/proposals/2026-11_nlrc-ai-labor-commission/제안요청_준수표.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="104" customHeight="1">
+    <row r="4" ht="118" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CSR-001</t>
@@ -556,12 +556,13 @@
 Ⅱ. 전략 및 방법론 &gt; 1.3.1 제안의 목적과 범위
 Ⅱ. 전략 및 방법론 &gt; 2.2.1 AI 노동위원회 · 노사마루 통합 추진 단계
 Ⅱ. 전략 및 방법론 &gt; 2.2.2 1차 산출물 인수 및 1차 사업 연속성 확보
+Ⅱ. 전략 및 방법론 &gt; 2.3.3 미확정 조건별 대응 방안 ② 측정 · 범위 · 작업장소
 Ⅷ. 기타 사항 &gt; 2.1.2 3차 사업계획 및 제안요청서 작성 (CSR-001)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>15~18, 21~22, 85</t>
+          <t>15~18, 21~22, 25, 87</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -571,7 +572,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr"/>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>ECR-001</t>
@@ -585,13 +586,14 @@
       <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
+Ⅱ. 전략 및 방법론 &gt; 2.3.2 미확정 조건별 대응 방안 ① 인프라 · 언어모델
 Ⅲ. 기술 및 기능 &gt; 1.1.1 별도 장비 확장 없는 자원 구성 및 최적화 방안
 Ⅲ. 기술 및 기능 &gt; 1.1.2 GPU 자원 배치 및 신규 기능 수용 방안</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>17, 29~30</t>
+          <t>17, 24, 31~32</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -621,7 +623,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>18~19, 42</t>
+          <t>18~19, 44</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -649,7 +651,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -677,7 +679,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -705,7 +707,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -733,7 +735,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -761,7 +763,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -791,7 +793,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>25, 44, 65</t>
+          <t>27, 46, 67</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -819,7 +821,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>25, 46</t>
+          <t>27, 48</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -877,7 +879,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>25, 47</t>
+          <t>27, 49</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -905,7 +907,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -933,7 +935,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -961,7 +963,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -989,7 +991,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1017,7 +1019,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1045,7 +1047,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1074,7 +1076,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>24, 31</t>
+          <t>26, 33</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1102,7 +1104,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1130,7 +1132,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>24, 30, 35</t>
+          <t>26, 32, 37</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1170,7 +1172,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="48" customHeight="1">
+    <row r="26" ht="62" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
           <t>SFR-021</t>
@@ -1183,14 +1185,15 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Ⅱ. 전략 및 방법론 &gt; 3.1.1 문서 전처리 개선 · Graph DB · 문서초안 고도화 기술
+          <t>Ⅱ. 전략 및 방법론 &gt; 2.3.2 미확정 조건별 대응 방안 ① 인프라 · 언어모델
+Ⅱ. 전략 및 방법론 &gt; 3.1.1 문서 전처리 개선 · Graph DB · 문서초안 고도화 기술
 Ⅲ. 기술 및 기능 &gt; 1.1.2 GPU 자원 배치 및 신규 기능 수용 방안
 Ⅲ. 기술 및 기능 &gt; 2.2.2 언어모델 성능 고도화</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>24, 30, 36</t>
+          <t>24, 26, 32, 38</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -1218,7 +1221,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1246,7 +1249,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1274,7 +1277,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1302,7 +1305,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1330,7 +1333,7 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1359,7 +1362,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>30, 40</t>
+          <t>32, 42</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -1387,7 +1390,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -1415,7 +1418,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -1443,7 +1446,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -1453,7 +1456,7 @@
       </c>
       <c r="F35" s="6" t="inlineStr"/>
     </row>
-    <row r="36" ht="34" customHeight="1">
+    <row r="36" ht="62" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
           <t>PER-002</t>
@@ -1467,12 +1470,14 @@
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
+Ⅱ. 전략 및 방법론 &gt; 2.3.2 미확정 조건별 대응 방안 ① 인프라 · 언어모델
+Ⅱ. 전략 및 방법론 &gt; 2.3.3 미확정 조건별 대응 방안 ② 측정 · 범위 · 작업장소
 Ⅳ. 성능 및 품질 &gt; 1.1.1 1차 사업 대비 평균 처리시간 30% 이상 단축 방안</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>17, 58</t>
+          <t>17, 24~25, 60</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -1482,7 +1487,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr"/>
     </row>
-    <row r="37" ht="34" customHeight="1">
+    <row r="37" ht="48" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>PER-003</t>
@@ -1496,12 +1501,13 @@
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Ⅱ. 전략 및 방법론 &gt; 1.2.2 1차 사업 대비 2차 사업 비교
+Ⅱ. 전략 및 방법론 &gt; 2.3.3 미확정 조건별 대응 방안 ② 측정 · 범위 · 작업장소
 Ⅳ. 성능 및 품질 &gt; 1.2.1 대용량 첨부파일 처리 · 토큰 한계로 인한 품질 저하 방지</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>17, 59</t>
+          <t>17, 25, 61</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -1529,7 +1535,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -1557,7 +1563,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -1585,7 +1591,7 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
@@ -1613,7 +1619,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -1644,7 +1650,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>19, 25, 64~65</t>
+          <t>19, 27, 66~67</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -1673,7 +1679,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>52, 70</t>
+          <t>54, 72</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1702,7 +1708,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>50, 52</t>
+          <t>52, 54</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1730,7 +1736,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
@@ -1758,7 +1764,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -1786,7 +1792,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -1814,7 +1820,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -1842,7 +1848,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -1870,7 +1876,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -1898,7 +1904,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -1926,7 +1932,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -1955,7 +1961,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>62~63</t>
+          <t>64~65</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -1983,7 +1989,7 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -2011,7 +2017,7 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2039,7 +2045,7 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -2067,7 +2073,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2095,7 +2101,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2123,7 +2129,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2152,7 +2158,7 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>50, 79</t>
+          <t>52, 81</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2181,7 +2187,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>49~50</t>
+          <t>51~52</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2210,7 +2216,7 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>61, 75</t>
+          <t>63, 77</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -2238,7 +2244,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -2266,7 +2272,7 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -2294,7 +2300,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -2322,7 +2328,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -2351,7 +2357,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>26, 55</t>
+          <t>28, 57</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -2379,7 +2385,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -2408,7 +2414,7 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>26, 56</t>
+          <t>28, 58</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -2436,7 +2442,7 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -2466,7 +2472,7 @@
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>22, 56, 79</t>
+          <t>22, 58, 81</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -2496,7 +2502,7 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>11, 13, 70</t>
+          <t>11, 13, 72</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -2554,7 +2560,7 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>12, 81</t>
+          <t>12, 83</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2582,7 +2588,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -2610,7 +2616,7 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -2638,7 +2644,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2668,7 +2674,7 @@
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>27, 68~69</t>
+          <t>29, 70~71</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
@@ -2696,7 +2702,7 @@
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
@@ -2724,7 +2730,7 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
@@ -2752,7 +2758,7 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
@@ -2780,7 +2786,7 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
@@ -2809,7 +2815,7 @@
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>22, 77</t>
+          <t>22, 79</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
@@ -2837,7 +2843,7 @@
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
@@ -2866,7 +2872,7 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>70, 83</t>
+          <t>72, 85</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
@@ -2894,7 +2900,7 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2904,7 +2910,7 @@
       </c>
       <c r="F86" s="6" t="inlineStr"/>
     </row>
-    <row r="87" ht="20" customHeight="1">
+    <row r="87" ht="34" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
           <t>PSR-007</t>
@@ -2917,12 +2923,13 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Ⅴ. 프로젝트 관리 &gt; 4.1.1 작업장소 · 개발환경 준비 및 원격지 보안대책</t>
+          <t>Ⅱ. 전략 및 방법론 &gt; 2.3.3 미확정 조건별 대응 방안 ② 측정 · 범위 · 작업장소
+Ⅴ. 프로젝트 관리 &gt; 4.1.1 작업장소 · 개발환경 준비 및 원격지 보안대책</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>25, 74</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
